--- a/Companies/Robustness_150_Portfolio_Selection.xlsx
+++ b/Companies/Robustness_150_Portfolio_Selection.xlsx
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.5614306874365028</v>
+        <v>0.5614306216407438</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.004382633024868077</v>
+        <v>0.004382567229109013</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.5510172543666143</v>
+        <v>0.5510171795489196</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.006030800045020435</v>
+        <v>0.006030874862715141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.5486087595882563</v>
+        <v>0.5486085130344404</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.008439294823378463</v>
+        <v>0.008439541377194382</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.5480437665678705</v>
+        <v>0.5480436870973399</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.00900428784376428</v>
+        <v>0.009004367314294881</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.5673572857100418</v>
+        <v>0.5673574265329032</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.01030923129840711</v>
+        <v>0.01030937212126848</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.5407071558642456</v>
+        <v>0.5407071294418819</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.01634089854738918</v>
+        <v>0.01634092496975281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.5398027488219184</v>
+        <v>0.5398025017949174</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.01724530558971638</v>
+        <v>0.01724555261671734</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.5390378921099448</v>
+        <v>0.5390380204607657</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.01801016230168995</v>
+        <v>0.01801003395086909</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.537790118991479</v>
+        <v>0.5377902042436242</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.01925793542015575</v>
+        <v>0.01925785016801052</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.5354125863565242</v>
+        <v>0.5354125571230512</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.02163546805511052</v>
+        <v>0.02163549728858349</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.5349899066156441</v>
+        <v>0.5349901102947543</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.02205814779599069</v>
+        <v>0.02205794411688045</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.5349541460440944</v>
+        <v>0.5349541782247231</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.02209390836754033</v>
+        <v>0.02209387618691161</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.531620248800356</v>
+        <v>0.5316202033509291</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.02542780561127878</v>
+        <v>0.02542785106070566</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.5315000106678174</v>
+        <v>0.5315001781872758</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.02554804374381736</v>
+        <v>0.02554787622435895</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.5310783146697015</v>
+        <v>0.5310781169485047</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.02596973974193328</v>
+        <v>0.02596993746313003</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.5310612702452693</v>
+        <v>0.5310614141816882</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.02598678416636546</v>
+        <v>0.02598664022994657</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.5304366310942528</v>
+        <v>0.5304367026288034</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.02661142331738198</v>
+        <v>0.02661135178283136</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1084,13 +1084,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.5293289206543967</v>
+        <v>0.5293290917351942</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.027719133757238</v>
+        <v>0.02771896267644058</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.5281437528994116</v>
+        <v>0.5281437964021996</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.02890430151222312</v>
+        <v>0.02890425800943519</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1136,13 +1136,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.5280291360780208</v>
+        <v>0.5280292273194572</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.02901891833361392</v>
+        <v>0.02901882709217751</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.5274082058276757</v>
+        <v>0.5274081763910249</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.02963984858395907</v>
+        <v>0.02963987802060986</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.5271378734475702</v>
+        <v>0.5271378561949772</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.0299101809640645</v>
+        <v>0.02991019821665752</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.5268952599033069</v>
+        <v>0.5268951077184602</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.03015279450832786</v>
+        <v>0.03015294669317459</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.5264845201148952</v>
+        <v>0.5264844468645761</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.03056353429673953</v>
+        <v>0.03056360754705867</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.524087054516476</v>
+        <v>0.5240870407875293</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.03296099989515877</v>
+        <v>0.03296101362410542</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.5230625868337995</v>
+        <v>0.5230627238339044</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.03398546757783527</v>
+        <v>0.03398533057773034</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1318,13 +1318,13 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.5229022065493594</v>
+        <v>0.5229022977774342</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.03414584786227537</v>
+        <v>0.0341457566342005</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.521866716816676</v>
+        <v>0.5218668153958471</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.03518133759495878</v>
+        <v>0.03518123901578762</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.5205025602297866</v>
+        <v>0.5205024818839468</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.03654549418184816</v>
+        <v>0.03654557252768798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.5197742250742005</v>
+        <v>0.5197739436493117</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.03727382933743428</v>
+        <v>0.03727411076232301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1422,13 +1422,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.5190176033536843</v>
+        <v>0.5190173707778639</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.03803045105795044</v>
+        <v>0.03803068363377082</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1448,13 +1448,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.5187863901960635</v>
+        <v>0.5187863274662387</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.0382616642155712</v>
+        <v>0.03826172694539609</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.5181312283060359</v>
+        <v>0.5181309959758936</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.03891682610559888</v>
+        <v>0.03891705843574111</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.5176685528332</v>
+        <v>0.5176685553665636</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.03937950157843473</v>
+        <v>0.0393794990450711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.5170668922828404</v>
+        <v>0.5170668854802309</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.03998116212879432</v>
+        <v>0.0399811689314038</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.5165324009867138</v>
+        <v>0.5165325877512552</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.04051565342492092</v>
+        <v>0.04051546666037953</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0.5165071723017282</v>
+        <v>0.5165071157755052</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.04054088210990658</v>
+        <v>0.04054093863612951</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1604,13 +1604,13 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>0.5163990587686205</v>
+        <v>0.5163990764370255</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.04064899564301427</v>
+        <v>0.0406489779746092</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1630,13 +1630,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.5162789629204367</v>
+        <v>0.5162788623590463</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.04076909149119801</v>
+        <v>0.04076919205258844</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.5150722145758085</v>
+        <v>0.5150722204473962</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.0419758398358262</v>
+        <v>0.04197583396423854</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.5149256644835866</v>
+        <v>0.514925647886965</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.04212238992804818</v>
+        <v>0.0421224065246697</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1708,13 +1708,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0.5147828585201729</v>
+        <v>0.514782870616877</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.04226519589146183</v>
+        <v>0.04226518379475774</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1734,13 +1734,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.5147172860286298</v>
+        <v>0.5147173770986181</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.04233076838300498</v>
+        <v>0.04233067731301665</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.5144509929211448</v>
+        <v>0.5144511156045121</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.04259706149048992</v>
+        <v>0.04259693880712268</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>0.5143427116824891</v>
+        <v>0.514342781786872</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.04270534272914561</v>
+        <v>0.04270527262476276</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1812,13 +1812,13 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>0.5142997715187869</v>
+        <v>0.5142995865042378</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.04274828289284782</v>
+        <v>0.04274846790739695</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>0.5139504756514479</v>
+        <v>0.513950465133068</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.04309757876018683</v>
+        <v>0.04309758927856677</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.5138508836101894</v>
+        <v>0.5138508673526011</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.04319717080144536</v>
+        <v>0.04319718705903364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1890,13 +1890,13 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.5135562282070409</v>
+        <v>0.5135564156852435</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.0434918262045938</v>
+        <v>0.04349163872639128</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>0.5132573646526046</v>
+        <v>0.5132575245094996</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0.5570480544116347</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.04379068975903011</v>
+        <v>0.04379052990213517</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>0.3036097204502829</v>
+        <v>0.3036095602237834</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>7.818465693754106e-07</v>
+        <v>6.216200698072605e-07</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0.3036097984893236</v>
+        <v>0.3036097933095506</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>8.598856100494601e-07</v>
+        <v>8.547058369945404e-07</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.3036098017290116</v>
+        <v>0.3036098964099827</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>8.63125298011802e-07</v>
+        <v>9.578062691306677e-07</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>0.3036071632511997</v>
+        <v>0.303607138117879</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1.775352513833095e-06</v>
+        <v>1.800485834591026e-06</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>0.3036107946127035</v>
+        <v>0.3036109574783026</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1.856008989886693e-06</v>
+        <v>2.01887458906036e-06</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>0.303606894786713</v>
+        <v>0.3036068670206591</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2.043817000585424e-06</v>
+        <v>2.071583054430448e-06</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>0.3036061057815507</v>
+        <v>0.3036062190933286</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2.832822162901483e-06</v>
+        <v>2.719510384940893e-06</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>0.3036059187212203</v>
+        <v>0.3036059134328022</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>3.019882493293657e-06</v>
+        <v>3.025170911385988e-06</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>0.3036056449040583</v>
+        <v>0.3036057513476966</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>3.293699655237958e-06</v>
+        <v>3.187256017000983e-06</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2176,17 +2176,17 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>0.3036127615577649</v>
+        <v>0.3036051289020325</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>3.822954051324601e-06</v>
+        <v>3.809701681067867e-06</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ADI, AMT, DVN, F, GLW, KDP, KMX, KSS, NRG, SLB</t>
+          <t>CPB, DUK, EMR, EXC, FFIV, FLR, HAS, JNJ, PFG, TSN</t>
         </is>
       </c>
     </row>
@@ -2202,17 +2202,17 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>0.303605051243995</v>
+        <v>0.3036127636664828</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>3.887359718568462e-06</v>
+        <v>3.825062769191589e-06</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CPB, DUK, EMR, EXC, FFIV, FLR, HAS, JNJ, PFG, TSN</t>
+          <t>ADI, AMT, DVN, F, GLW, KDP, KMX, KSS, NRG, SLB</t>
         </is>
       </c>
     </row>
@@ -2228,17 +2228,17 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>0.3036133568742025</v>
+        <v>0.3036045325229687</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>4.418270488970588e-06</v>
+        <v>4.406080744923102e-06</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ADSK, BAC, CSCO, DTE, ETN, HBAN, HOG, HUM, LUV, MKC</t>
+          <t>AMT, DRI, FDX, HAS, NTAP, OMC, PEP, PG, PRU, SRE</t>
         </is>
       </c>
     </row>
@@ -2254,13 +2254,13 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>0.3036044952738776</v>
+        <v>0.3036045075561462</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4.443329836012477e-06</v>
+        <v>4.431047567365898e-06</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2280,17 +2280,17 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>0.3036041197833209</v>
+        <v>0.3036134346017647</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>4.818820392660239e-06</v>
+        <v>4.495998051079475e-06</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AMT, DRI, FDX, HAS, NTAP, OMC, PEP, PG, PRU, SRE</t>
+          <t>ADSK, BAC, CSCO, DTE, ETN, HBAN, HOG, HUM, LUV, MKC</t>
         </is>
       </c>
     </row>
@@ -2306,17 +2306,17 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>0.3036040210834569</v>
+        <v>0.3036039507841418</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>4.917520256719765e-06</v>
+        <v>4.987819571755647e-06</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BAC, CTSH, DUK, KEY, LNC, MUR, NKE, PHM, PNW, TJX</t>
+          <t>AZO, BMY, EXC, FCX, GIS, GPC, MRK, PEP, PFG, ROST</t>
         </is>
       </c>
     </row>
@@ -2332,17 +2332,17 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>0.3036139645302801</v>
+        <v>0.303603919381003</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>5.025926566537553e-06</v>
+        <v>5.019222710622717e-06</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ABT, CMCSA, EBAY, GHC, ITW, MCK, NRG, PCAR, WMB, XEL</t>
+          <t>BAC, CTSH, DUK, KEY, LNC, MUR, NKE, PHM, PNW, TJX</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0.3036035216047822</v>
+        <v>0.3036142570262282</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>5.416998931362382e-06</v>
+        <v>5.318422514666299e-06</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AZO, BMY, EXC, FCX, GIS, GPC, MRK, PEP, PFG, ROST</t>
+          <t>ABT, CMCSA, EBAY, GHC, ITW, MCK, NRG, PCAR, WMB, XEL</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>0.3036148715779662</v>
+        <v>0.3036148012398673</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>5.932974252609302e-06</v>
+        <v>5.862636153763923e-06</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2410,13 +2410,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.3036028263146368</v>
+        <v>0.3036028705106291</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>6.112289076765087e-06</v>
+        <v>6.068093084510284e-06</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2436,17 +2436,17 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>0.3036152266178834</v>
+        <v>0.3036025948681121</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>6.288014169852918e-06</v>
+        <v>6.343735601432865e-06</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>COP, DHR, GOOGL, KDP, MSI, MTB, NRG, PAYX, PRU, WYNN</t>
+          <t>CAT, CF, IFF, NBR, PG, PSX, SHW, THC, VLO, VMC</t>
         </is>
       </c>
     </row>
@@ -2462,17 +2462,17 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>0.3036025455234336</v>
+        <v>0.30361532260653</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>6.393080279942787e-06</v>
+        <v>6.384002816384182e-06</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CAT, CF, IFF, NBR, PG, PSX, SHW, THC, VLO, VMC</t>
+          <t>COP, DHR, GOOGL, KDP, MSI, MTB, NRG, PAYX, PRU, WYNN</t>
         </is>
       </c>
     </row>
@@ -2488,17 +2488,17 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>0.3036024113450927</v>
+        <v>0.3036022968472697</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>6.527258620825371e-06</v>
+        <v>6.64175644388143e-06</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AMGN, EIX, FLR, LOW, NUE, PCAR, PSA, ROK, SCHW, WYNN</t>
+          <t>EBAY, EIX, GHC, HAL, IRM, JNJ, L, LLY, PLD, SYY</t>
         </is>
       </c>
     </row>
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>0.3036023433924013</v>
+        <v>0.3036022708438711</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>6.595211312299121e-06</v>
+        <v>6.667759842426957e-06</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2540,17 +2540,17 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>0.3036022923365265</v>
+        <v>0.3036156556280282</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>6.646267187104815e-06</v>
+        <v>6.71702431459531e-06</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>EBAY, EIX, GHC, HAL, IRM, JNJ, L, LLY, PLD, SYY</t>
+          <t>AMD, BF-B, CCI, CSCO, DHR, IRM, MA, MDT, RSG, SNA</t>
         </is>
       </c>
     </row>
@@ -2566,17 +2566,17 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>0.3036156753162147</v>
+        <v>0.3036022203562972</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>6.736712501120845e-06</v>
+        <v>6.718247416381828e-06</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AMD, BF-B, CCI, CSCO, DHR, IRM, MA, MDT, RSG, SNA</t>
+          <t>AMGN, EIX, FLR, LOW, NUE, PCAR, PSA, ROK, SCHW, WYNN</t>
         </is>
       </c>
     </row>
@@ -2592,13 +2592,13 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>0.3036163168567225</v>
+        <v>0.3036162310404634</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>7.378253008893942e-06</v>
+        <v>7.292436749795073e-06</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>0.3036010728651947</v>
+        <v>0.3036012708321368</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>7.865738518908483e-06</v>
+        <v>7.667771576791438e-06</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>0.30360057367196</v>
+        <v>0.3036004694432785</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>8.364931753546134e-06</v>
+        <v>8.469160435065071e-06</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>0.303617345486313</v>
+        <v>0.3036174450684476</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>8.406882599398813e-06</v>
+        <v>8.506464734048258e-06</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2696,17 +2696,17 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>0.3036179520850379</v>
+        <v>0.3036001576730011</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>9.013481324315897e-06</v>
+        <v>8.780930712437574e-06</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AAPL, ADSK, ALL, AON, CCI, CL, FLS, NVDA, PEG, PRGO</t>
+          <t>COF, DVA, EXPE, FIS, FITB, KDP, ORLY, UNH, XEL, XRAY</t>
         </is>
       </c>
     </row>
@@ -2722,17 +2722,17 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>0.3035998755912239</v>
+        <v>0.303617816263383</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>9.063012489707312e-06</v>
+        <v>8.877659669392912e-06</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>COF, DVA, EXPE, FIS, FITB, KDP, ORLY, UNH, XEL, XRAY</t>
+          <t>AAPL, ADSK, ALL, AON, CCI, CL, FLS, NVDA, PEG, PRGO</t>
         </is>
       </c>
     </row>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>0.3036184463185894</v>
+        <v>0.3036183915418371</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>9.507714875844897e-06</v>
+        <v>9.452938123488686e-06</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2774,13 +2774,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>0.3035992878716774</v>
+        <v>0.3035991801095758</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>9.650732036126097e-06</v>
+        <v>9.75849413775709e-06</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2800,13 +2800,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>0.3035990971225389</v>
+        <v>0.3035989005187061</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>9.8414811746661e-06</v>
+        <v>1.003808500743553e-05</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>0.3036191041831836</v>
+        <v>0.3036190479311184</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1.016557947003394e-05</v>
+        <v>1.010932740480586e-05</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2852,17 +2852,17 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>0.3036192792718427</v>
+        <v>0.3036192941378936</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>1.034066812916068e-05</v>
+        <v>1.035553418005097e-05</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BF-B, BMY, EFX, GILD, HBAN, NWL, SCHW, SRE, VNO, ZION</t>
+          <t>AEE, DUK, FDX, GHC, PAYX, PPG, ROK, TER, TMUS, ZBH</t>
         </is>
       </c>
     </row>
@@ -2878,17 +2878,17 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>0.3036193010416527</v>
+        <v>0.3036193821365382</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>1.03624379391154e-05</v>
+        <v>1.044353282464439e-05</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AEE, DUK, FDX, GHC, PAYX, PPG, ROK, TER, TMUS, ZBH</t>
+          <t>BF-B, BMY, EFX, GILD, HBAN, NWL, SCHW, SRE, VNO, ZION</t>
         </is>
       </c>
     </row>
@@ -2904,13 +2904,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>0.3035981327095886</v>
+        <v>0.3035982065688012</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>1.080589412494337e-05</v>
+        <v>1.073203491236407e-05</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>0.3035979526636726</v>
+        <v>0.303597919122969</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>1.098594004095288e-05</v>
+        <v>1.101948074461179e-05</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2956,13 +2956,13 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>0.3035972025149692</v>
+        <v>0.3035973807583779</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1.173608874432963e-05</v>
+        <v>1.155784533568571e-05</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>0.303597172248812</v>
+        <v>0.3035972638894585</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>1.176635490157674e-05</v>
+        <v>1.167471425506106e-05</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>0.3035970397827402</v>
+        <v>0.3035970098292363</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>1.189882097335504e-05</v>
+        <v>1.192877447725449e-05</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3034,13 +3034,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>0.3036209661801849</v>
+        <v>0.3036209701997956</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1.202757647134067e-05</v>
+        <v>1.203159608204052e-05</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3060,13 +3060,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>0.3035969003767457</v>
+        <v>0.303596902831126</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.203822696782542e-05</v>
+        <v>1.203577258757083e-05</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>0.3035964500304496</v>
+        <v>0.303596518699233</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1.248857326396902e-05</v>
+        <v>1.241990448058727e-05</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3112,17 +3112,17 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>0.3036218467553794</v>
+        <v>0.3035960815410351</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.290815166582471e-05</v>
+        <v>1.285706267845077e-05</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>COST, DXC, EOG, FLR, HRL, IBM, JEF, JNJ, MTB, NBR</t>
+          <t>ADSK, AMD, BEN, CB, DGX, GIS, IFF, SBUX, USB, VIAV</t>
         </is>
       </c>
     </row>
@@ -3138,17 +3138,17 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>0.3035959342863864</v>
+        <v>0.303621897052346</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.300431732714769e-05</v>
+        <v>1.295844863241635e-05</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ADSK, AMD, BEN, CB, DGX, GIS, IFF, SBUX, USB, VIAV</t>
+          <t>COST, DXC, EOG, FLR, HRL, IBM, JEF, JNJ, MTB, NBR</t>
         </is>
       </c>
     </row>
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>0.3036219771329512</v>
+        <v>0.3036220909166529</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1.303852923767446e-05</v>
+        <v>1.315231293935737e-05</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3190,13 +3190,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>0.3035957395641007</v>
+        <v>0.3035955876110032</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1.319903961283231e-05</v>
+        <v>1.335099271038143e-05</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>0.3036222901395687</v>
+        <v>0.3036223690132517</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0.3036089386037136</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1.335153585513282e-05</v>
+        <v>1.343040953810659e-05</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>0.1120943044524251</v>
+        <v>0.1120943114599232</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0.01057118324396208</v>
+        <v>0.01057119025146018</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3268,13 +3268,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>0.1194720521532189</v>
+        <v>0.1194721266741575</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0.01794893094475589</v>
+        <v>0.01794900546569453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3294,13 +3294,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>0.1205146842542632</v>
+        <v>0.1205147367800031</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0.01899156304580021</v>
+        <v>0.0189916155715401</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3320,13 +3320,13 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>0.1208498676354552</v>
+        <v>0.1208499424507176</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.01932674642699218</v>
+        <v>0.01932682124225456</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3346,13 +3346,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>0.1241273440447277</v>
+        <v>0.1241271377729871</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0.02260422283626469</v>
+        <v>0.02260401656452414</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>0.1248561250756547</v>
+        <v>0.1248560280758878</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>0.02333300386719173</v>
+        <v>0.02333290686742481</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3398,13 +3398,13 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>0.1251250708617704</v>
+        <v>0.1251250127888969</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>0.02360194965330738</v>
+        <v>0.0236018915804339</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>0.1262892293187165</v>
+        <v>0.1262892259934839</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>0.02476610811025352</v>
+        <v>0.02476610478502091</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3450,13 +3450,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>0.128306071994749</v>
+        <v>0.1283061075296311</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0.02678295078628602</v>
+        <v>0.02678298632116809</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3476,13 +3476,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>0.1296591833584221</v>
+        <v>0.1296590749842121</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.02813606214995913</v>
+        <v>0.02813595377574908</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>0.1300054003488753</v>
+        <v>0.1300051983715465</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0.02848227914041231</v>
+        <v>0.0284820771630835</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3528,13 +3528,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>0.1314827879652146</v>
+        <v>0.1314826084126619</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0.02995966675675159</v>
+        <v>0.0299594872041989</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3554,13 +3554,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>0.1316091477918114</v>
+        <v>0.1316091076711429</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0.0300860265833484</v>
+        <v>0.03008598646267986</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3580,13 +3580,13 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>0.1320053784815412</v>
+        <v>0.1320053413338185</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.0304822572730782</v>
+        <v>0.03048222012535549</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>0.1327596579788921</v>
+        <v>0.1327596858753369</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0.03123653677042905</v>
+        <v>0.03123656466687387</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -3632,13 +3632,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>0.1331130902868891</v>
+        <v>0.1331129470388484</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0.03158996907842608</v>
+        <v>0.03158982583038535</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>0.133249077741526</v>
+        <v>0.1332493444466442</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0.03172595653306297</v>
+        <v>0.03172622323818121</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>0.1344583445186908</v>
+        <v>0.1344583338334136</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0.03293522331022776</v>
+        <v>0.03293521262495062</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>0.1350843564011331</v>
+        <v>0.1350842964700847</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.03356123519267008</v>
+        <v>0.03356117526162171</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>0.1352324753198886</v>
+        <v>0.1352324675734086</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0.0337093541114256</v>
+        <v>0.03370934636494556</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -3762,13 +3762,13 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>0.1353211161675785</v>
+        <v>0.1353209656407475</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0.03379799495911547</v>
+        <v>0.03379784443228452</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>0.1359806229291021</v>
+        <v>0.1359806087192088</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>0.03445750172063909</v>
+        <v>0.03445748751074575</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -3814,13 +3814,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>0.1366010982433383</v>
+        <v>0.1366009421591258</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0.03507797703487529</v>
+        <v>0.03507782095066279</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -3840,13 +3840,13 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>0.1368276115799257</v>
+        <v>0.1368276213052288</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0.03530449037146267</v>
+        <v>0.03530450009676582</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>0.1370269028401652</v>
+        <v>0.1370267042243554</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>0.03550378163170224</v>
+        <v>0.03550358301589236</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>0.1373694342362057</v>
+        <v>0.1373692640692507</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>0.0358463130277427</v>
+        <v>0.0358461428607877</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -3918,13 +3918,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>0.1376383238324941</v>
+        <v>0.1376384828516599</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>0.0361152026240311</v>
+        <v>0.03611536164319688</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>0.1378283092053575</v>
+        <v>0.137828297399756</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>0.03630518799689446</v>
+        <v>0.03630517619129296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -3970,13 +3970,13 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>0.1381094306450709</v>
+        <v>0.1381094392821494</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0.03658630943660786</v>
+        <v>0.03658631807368641</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -3996,13 +3996,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>0.1381988800839057</v>
+        <v>0.1381987713128701</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>0.03667575887544273</v>
+        <v>0.03667565010440711</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -4022,13 +4022,13 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>0.1383748705932277</v>
+        <v>0.1383749402251984</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0.03685174938476467</v>
+        <v>0.03685181901673541</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -4048,13 +4048,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>0.1384938099268651</v>
+        <v>0.1384937126074141</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>0.03697068871840208</v>
+        <v>0.03697059139895108</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -4074,13 +4074,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>0.1385147917619704</v>
+        <v>0.1385146521242338</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>0.03699167055350742</v>
+        <v>0.03699153091577075</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -4100,13 +4100,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>0.1387310654674445</v>
+        <v>0.1387309709699497</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>0.03720794425898145</v>
+        <v>0.03720784976148671</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4126,13 +4126,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>0.1387715979554244</v>
+        <v>0.138771576355699</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>0.0372484767469614</v>
+        <v>0.037248455147236</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>0.1388455002342885</v>
+        <v>0.1388454964505395</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>0.03732237902582548</v>
+        <v>0.03732237524207653</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -4178,13 +4178,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>0.138909800421821</v>
+        <v>0.1389098629451858</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>0.03738667921335796</v>
+        <v>0.03738674173672275</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -4204,13 +4204,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>0.1393254192891236</v>
+        <v>0.1393253755622721</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>0.03780229808066059</v>
+        <v>0.03780225435380906</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -4230,13 +4230,13 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>0.1398821945846692</v>
+        <v>0.1398822640819277</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>0.03835907337620618</v>
+        <v>0.03835914287346469</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>0.140052379783681</v>
+        <v>0.1400524964603359</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.03852925857521804</v>
+        <v>0.03852937525187293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -4282,13 +4282,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>0.1402934329426243</v>
+        <v>0.1402935171246951</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>0.0387703117341613</v>
+        <v>0.03877039591623212</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -4308,13 +4308,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>0.1403171564090533</v>
+        <v>0.1403170690270905</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>0.03879403520059031</v>
+        <v>0.03879394781862745</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -4334,13 +4334,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>0.1403362595325254</v>
+        <v>0.1403363098871012</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>0.03881313832406237</v>
+        <v>0.03881318867863819</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -4360,13 +4360,13 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>0.140429565526748</v>
+        <v>0.1404294995787818</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.03890644431828504</v>
+        <v>0.03890637837031878</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -4386,13 +4386,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>0.1404464671355015</v>
+        <v>0.1404464258108138</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>0.03892334592703851</v>
+        <v>0.03892330460235084</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>0.1407130091965804</v>
+        <v>0.1407130237845473</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>0.03918988798811736</v>
+        <v>0.03918990257608425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>0.1407708604575291</v>
+        <v>0.1407710055810754</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>0.03924773924906609</v>
+        <v>0.03924788437261235</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -4464,13 +4464,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>0.1409659214033917</v>
+        <v>0.1409658555926888</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>0.03944280019492867</v>
+        <v>0.03944273438422576</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -4490,13 +4490,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>0.1410826786056689</v>
+        <v>0.1410827735801753</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0.03955955739720594</v>
+        <v>0.03955965237171234</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -4516,13 +4516,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>0.1411173002736791</v>
+        <v>0.1411171894037501</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>0.101523121208463</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>0.0395941790652161</v>
+        <v>0.03959406819528709</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>CPB</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>DUK</t>
         </is>
       </c>
     </row>
@@ -14644,7 +14644,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>EMR</t>
         </is>
       </c>
     </row>
@@ -14661,7 +14661,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>FFIV</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>FLR</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>KMX</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>KSS</t>
+          <t>JNJ</t>
         </is>
       </c>
     </row>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>PFG</t>
         </is>
       </c>
     </row>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>TSN</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>CPB</t>
+          <t>ADI</t>
         </is>
       </c>
     </row>
@@ -14797,7 +14797,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>AMT</t>
         </is>
       </c>
     </row>
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>DVN</t>
         </is>
       </c>
     </row>
@@ -14831,7 +14831,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>GLW</t>
         </is>
       </c>
     </row>
@@ -14865,7 +14865,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>FLR</t>
+          <t>KDP</t>
         </is>
       </c>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>KMX</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>KSS</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>NRG</t>
         </is>
       </c>
     </row>
@@ -14933,7 +14933,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>SLB</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>AMT</t>
         </is>
       </c>
     </row>
@@ -14967,7 +14967,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>DRI</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>FDX</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>DTE</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>NTAP</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>OMC</t>
         </is>
       </c>
     </row>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>HOG</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>LUV</t>
+          <t>PRU</t>
         </is>
       </c>
     </row>
@@ -15103,7 +15103,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>SRE</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>ADSK</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>BAC</t>
         </is>
       </c>
     </row>
@@ -15324,7 +15324,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>CSCO</t>
         </is>
       </c>
     </row>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>DTE</t>
         </is>
       </c>
     </row>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>ETN</t>
         </is>
       </c>
     </row>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>HBAN</t>
         </is>
       </c>
     </row>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>HOG</t>
         </is>
       </c>
     </row>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>HUM</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>LUV</t>
         </is>
       </c>
     </row>
@@ -15443,7 +15443,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>MKC</t>
         </is>
       </c>
     </row>
@@ -15460,7 +15460,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>AZO</t>
         </is>
       </c>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>BMY</t>
         </is>
       </c>
     </row>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>FCX</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>LNC</t>
+          <t>GIS</t>
         </is>
       </c>
     </row>
@@ -15545,7 +15545,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>GPC</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>MRK</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>PNW</t>
+          <t>PFG</t>
         </is>
       </c>
     </row>
@@ -15613,7 +15613,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>ROST</t>
         </is>
       </c>
     </row>
@@ -15630,7 +15630,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>BAC</t>
         </is>
       </c>
     </row>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>CTSH</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>DUK</t>
         </is>
       </c>
     </row>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>GHC</t>
+          <t>KEY</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>ITW</t>
+          <t>LNC</t>
         </is>
       </c>
     </row>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>MUR</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>NKE</t>
         </is>
       </c>
     </row>
@@ -15749,7 +15749,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>PHM</t>
         </is>
       </c>
     </row>
@@ -15766,7 +15766,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>PNW</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>TJX</t>
         </is>
       </c>
     </row>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>ABT</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>CMCSA</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>EBAY</t>
         </is>
       </c>
     </row>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>GHC</t>
         </is>
       </c>
     </row>
@@ -15868,7 +15868,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>ITW</t>
         </is>
       </c>
     </row>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>MCK</t>
         </is>
       </c>
     </row>
@@ -15902,7 +15902,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>NRG</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PCAR</t>
         </is>
       </c>
     </row>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>WMB</t>
         </is>
       </c>
     </row>
@@ -15953,7 +15953,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>XEL</t>
         </is>
       </c>
     </row>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CAT</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>CF</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>IFF</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>NBR</t>
         </is>
       </c>
     </row>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -16395,7 +16395,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>PSX</t>
         </is>
       </c>
     </row>
@@ -16412,7 +16412,7 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>SHW</t>
         </is>
       </c>
     </row>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>THC</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>VLO</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16463,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>VMC</t>
         </is>
       </c>
     </row>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>COP</t>
         </is>
       </c>
     </row>
@@ -16497,7 +16497,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>DHR</t>
         </is>
       </c>
     </row>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>KDP</t>
         </is>
       </c>
     </row>
@@ -16548,7 +16548,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>MSI</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>MTB</t>
         </is>
       </c>
     </row>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>NRG</t>
         </is>
       </c>
     </row>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>PAYX</t>
         </is>
       </c>
     </row>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>PRU</t>
         </is>
       </c>
     </row>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>WYNN</t>
         </is>
       </c>
     </row>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>EBAY</t>
         </is>
       </c>
     </row>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>FLR</t>
+          <t>GHC</t>
         </is>
       </c>
     </row>
@@ -16701,7 +16701,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HAL</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>IRM</t>
         </is>
       </c>
     </row>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>JNJ</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>PSA</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -16769,7 +16769,7 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>LLY</t>
         </is>
       </c>
     </row>
@@ -16786,7 +16786,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>PLD</t>
         </is>
       </c>
     </row>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>SYY</t>
         </is>
       </c>
     </row>
@@ -16990,7 +16990,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>AMD</t>
         </is>
       </c>
     </row>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>BF-B</t>
         </is>
       </c>
     </row>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>GHC</t>
+          <t>CCI</t>
         </is>
       </c>
     </row>
@@ -17041,7 +17041,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>CSCO</t>
         </is>
       </c>
     </row>
@@ -17058,7 +17058,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>DHR</t>
         </is>
       </c>
     </row>
@@ -17075,7 +17075,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>IRM</t>
         </is>
       </c>
     </row>
@@ -17092,7 +17092,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MDT</t>
         </is>
       </c>
     </row>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>RSG</t>
         </is>
       </c>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>SNA</t>
         </is>
       </c>
     </row>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AMGN</t>
         </is>
       </c>
     </row>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>BF-B</t>
+          <t>EIX</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>FLR</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>NUE</t>
         </is>
       </c>
     </row>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>PCAR</t>
         </is>
       </c>
     </row>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PSA</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>ROK</t>
         </is>
       </c>
     </row>
@@ -17296,7 +17296,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>SCHW</t>
         </is>
       </c>
     </row>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>WYNN</t>
         </is>
       </c>
     </row>
@@ -18010,7 +18010,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>COF</t>
         </is>
       </c>
     </row>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>DVA</t>
         </is>
       </c>
     </row>
@@ -18044,7 +18044,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>EXPE</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18061,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>FIS</t>
         </is>
       </c>
     </row>
@@ -18078,7 +18078,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>FITB</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18095,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>KDP</t>
         </is>
       </c>
     </row>
@@ -18112,7 +18112,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>FLS</t>
+          <t>ORLY</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>UNH</t>
         </is>
       </c>
     </row>
@@ -18146,7 +18146,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>XEL</t>
         </is>
       </c>
     </row>
@@ -18163,7 +18163,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>XRAY</t>
         </is>
       </c>
     </row>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>AAPL</t>
         </is>
       </c>
     </row>
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>DVA</t>
+          <t>ADSK</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>AON</t>
         </is>
       </c>
     </row>
@@ -18248,7 +18248,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>CCI</t>
         </is>
       </c>
     </row>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
@@ -18282,7 +18282,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>FLS</t>
         </is>
       </c>
     </row>
@@ -18299,7 +18299,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>NVDA</t>
         </is>
       </c>
     </row>
@@ -18316,7 +18316,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>PEG</t>
         </is>
       </c>
     </row>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>XRAY</t>
+          <t>PRGO</t>
         </is>
       </c>
     </row>
@@ -19030,7 +19030,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>BF-B</t>
+          <t>AEE</t>
         </is>
       </c>
     </row>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>DUK</t>
         </is>
       </c>
     </row>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>FDX</t>
         </is>
       </c>
     </row>
@@ -19081,7 +19081,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>GHC</t>
         </is>
       </c>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>PAYX</t>
         </is>
       </c>
     </row>
@@ -19115,7 +19115,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>NWL</t>
+          <t>PPG</t>
         </is>
       </c>
     </row>
@@ -19132,7 +19132,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ROK</t>
         </is>
       </c>
     </row>
@@ -19149,7 +19149,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>TER</t>
         </is>
       </c>
     </row>
@@ -19166,7 +19166,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>VNO</t>
+          <t>TMUS</t>
         </is>
       </c>
     </row>
@@ -19183,7 +19183,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>ZION</t>
+          <t>ZBH</t>
         </is>
       </c>
     </row>
@@ -19200,7 +19200,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>BF-B</t>
         </is>
       </c>
     </row>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>BMY</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>EFX</t>
         </is>
       </c>
     </row>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>GHC</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>HBAN</t>
         </is>
       </c>
     </row>
@@ -19285,7 +19285,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>NWL</t>
         </is>
       </c>
     </row>
@@ -19302,7 +19302,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>SCHW</t>
         </is>
       </c>
     </row>
@@ -19319,7 +19319,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>SRE</t>
         </is>
       </c>
     </row>
@@ -19336,7 +19336,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>VNO</t>
         </is>
       </c>
     </row>
@@ -19353,7 +19353,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>ZION</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>ADSK</t>
         </is>
       </c>
     </row>
@@ -20747,7 +20747,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>AMD</t>
         </is>
       </c>
     </row>
@@ -20764,7 +20764,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>BEN</t>
         </is>
       </c>
     </row>
@@ -20781,7 +20781,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>FLR</t>
+          <t>CB</t>
         </is>
       </c>
     </row>
@@ -20798,7 +20798,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>DGX</t>
         </is>
       </c>
     </row>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>GIS</t>
         </is>
       </c>
     </row>
@@ -20832,7 +20832,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>JEF</t>
+          <t>IFF</t>
         </is>
       </c>
     </row>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>SBUX</t>
         </is>
       </c>
     </row>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>USB</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>VIAV</t>
         </is>
       </c>
     </row>
@@ -20900,7 +20900,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>COST</t>
         </is>
       </c>
     </row>
@@ -20917,7 +20917,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DXC</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>EOG</t>
         </is>
       </c>
     </row>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>FLR</t>
         </is>
       </c>
     </row>
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>HRL</t>
         </is>
       </c>
     </row>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
@@ -21002,7 +21002,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>JEF</t>
         </is>
       </c>
     </row>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>JNJ</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>MTB</t>
         </is>
       </c>
     </row>
@@ -21053,7 +21053,7 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>VIAV</t>
+          <t>NBR</t>
         </is>
       </c>
     </row>
